--- a/data/performance/daily/signal_list_2026-05-29.xlsx
+++ b/data/performance/daily/signal_list_2026-05-29.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 37.5%  (6W / 10L of 16 evaluated, 1 pending)</t>
+          <t>Win Rate: 31.2%  (5W / 11L of 16 evaluated, 1 pending)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2020</v>
+        <v>1940</v>
       </c>
       <c r="D6" t="n">
         <v>1930</v>
@@ -585,10 +585,10 @@
         <v>2220</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.9</v>
+        <v>14.43</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-4.46</v>
+        <v>-0.52</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D7" t="n">
         <v>159</v>
@@ -627,10 +627,10 @@
         <v>160</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.91</v>
+        <v>2.56</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.27</v>
+        <v>1.92</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16925</v>
+        <v>17000</v>
       </c>
       <c r="D8" t="n">
         <v>16950</v>
@@ -669,14 +669,14 @@
         <v>17075</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.29</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1725</v>
+        <v>1735</v>
       </c>
       <c r="D11" t="n">
         <v>1740</v>
@@ -795,10 +795,10 @@
         <v>1750</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.45</v>
+        <v>0.86</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.87</v>
+        <v>0.29</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13225</v>
+        <v>13550</v>
       </c>
       <c r="D12" t="n">
         <v>12750</v>
@@ -837,10 +837,10 @@
         <v>13500</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.08</v>
+        <v>-0.37</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.59</v>
+        <v>-5.9</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="D13" t="n">
         <v>288</v>
@@ -879,10 +879,10 @@
         <v>288</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.88</v>
+        <v>2.13</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.88</v>
+        <v>2.13</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D14" t="n">
         <v>181</v>
@@ -921,10 +921,10 @@
         <v>252</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>15.6</v>
+        <v>18.87</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-16.97</v>
+        <v>-14.62</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D15" t="n">
         <v>226</v>
@@ -963,10 +963,10 @@
         <v>248</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-8.869999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="D17" t="n">
         <v>800</v>
@@ -1047,10 +1047,10 @@
         <v>820</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.44</v>
+        <v>-1.84</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4820</v>
+        <v>4830</v>
       </c>
       <c r="D19" t="n">
         <v>4790</v>
@@ -1131,10 +1131,10 @@
         <v>4820</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.62</v>
+        <v>-0.83</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="D20" t="n">
         <v>525</v>
@@ -1173,10 +1173,10 @@
         <v>525</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>19.32</v>
+        <v>24.41</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>19.32</v>
+        <v>24.41</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="D21" t="n">
         <v>450</v>
@@ -1215,10 +1215,10 @@
         <v>500</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-8.16</v>
+        <v>-10</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 30.4%  (14W / 32L of 46 evaluated, 2 pending)</t>
+          <t>Win Rate: 39.1%  (18W / 28L of 46 evaluated, 2 pending)</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2320</v>
+        <v>2330</v>
       </c>
       <c r="D6" t="n">
         <v>2760</v>
@@ -1391,10 +1391,10 @@
         <v>2910</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>25.43</v>
+        <v>24.89</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>18.97</v>
+        <v>18.45</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4070</v>
+        <v>4390</v>
       </c>
       <c r="D7" t="n">
         <v>3950</v>
@@ -1433,10 +1433,10 @@
         <v>4070</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0</v>
+        <v>-7.29</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.95</v>
+        <v>-10.02</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2020</v>
+        <v>1940</v>
       </c>
       <c r="D10" t="n">
         <v>1930</v>
@@ -1539,10 +1539,10 @@
         <v>2220</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.9</v>
+        <v>14.43</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.46</v>
+        <v>-0.52</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5800</v>
+        <v>5850</v>
       </c>
       <c r="D11" t="n">
         <v>6000</v>
@@ -1581,10 +1581,10 @@
         <v>6050</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.31</v>
+        <v>3.42</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.45</v>
+        <v>2.56</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>159</v>
@@ -1623,10 +1623,10 @@
         <v>160</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.91</v>
+        <v>2.56</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.27</v>
+        <v>1.92</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10100</v>
+        <v>10950</v>
       </c>
       <c r="D13" t="n">
         <v>9900</v>
@@ -1665,10 +1665,10 @@
         <v>10400</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.97</v>
+        <v>-5.02</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.98</v>
+        <v>-9.59</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1515</v>
+        <v>1500</v>
       </c>
       <c r="D14" t="n">
         <v>1665</v>
@@ -1707,10 +1707,10 @@
         <v>1690</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>11.55</v>
+        <v>12.67</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16925</v>
+        <v>17000</v>
       </c>
       <c r="D15" t="n">
         <v>16950</v>
@@ -1749,14 +1749,14 @@
         <v>17075</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.29</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="D17" t="n">
         <v>1130</v>
@@ -1833,10 +1833,10 @@
         <v>1150</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.88</v>
+        <v>1.32</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.88</v>
+        <v>-0.44</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1095</v>
+        <v>1040</v>
       </c>
       <c r="D19" t="n">
         <v>1100</v>
@@ -1917,10 +1917,10 @@
         <v>1300</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>18.72</v>
+        <v>25</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.46</v>
+        <v>5.77</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5200</v>
+        <v>4670</v>
       </c>
       <c r="D20" t="n">
         <v>4800</v>
@@ -1959,14 +1959,14 @@
         <v>5450</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.81</v>
+        <v>16.7</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-7.69</v>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.78</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3790</v>
+        <v>3740</v>
       </c>
       <c r="D22" t="n">
         <v>3720</v>
@@ -2043,10 +2043,10 @@
         <v>4020</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6.07</v>
+        <v>7.49</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.85</v>
+        <v>-0.53</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="D24" t="n">
         <v>505</v>
@@ -2127,14 +2127,14 @@
         <v>505</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0</v>
+        <v>9.31</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>9.31</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2990</v>
+        <v>3030</v>
       </c>
       <c r="D25" t="n">
         <v>2950</v>
@@ -2169,10 +2169,10 @@
         <v>3020</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1</v>
+        <v>-0.33</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.34</v>
+        <v>-2.64</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D26" t="n">
         <v>334</v>
@@ -2211,10 +2211,10 @@
         <v>356</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.71</v>
+        <v>5.95</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.76</v>
+        <v>-0.6</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="D27" t="n">
         <v>288</v>
@@ -2253,10 +2253,10 @@
         <v>288</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.88</v>
+        <v>2.13</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.88</v>
+        <v>2.13</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1955</v>
+        <v>1960</v>
       </c>
       <c r="D30" t="n">
         <v>1955</v>
@@ -2379,10 +2379,10 @@
         <v>1960</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D31" t="n">
         <v>181</v>
@@ -2421,10 +2421,10 @@
         <v>252</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>15.6</v>
+        <v>18.87</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-16.97</v>
+        <v>-14.62</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13000</v>
+        <v>12325</v>
       </c>
       <c r="D32" t="n">
         <v>12000</v>
@@ -2463,10 +2463,10 @@
         <v>13000</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-7.69</v>
+        <v>-2.64</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D34" t="n">
         <v>360</v>
@@ -2547,10 +2547,10 @@
         <v>426</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.97</v>
+        <v>6.5</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.45</v>
+        <v>-10</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D35" t="n">
         <v>226</v>
@@ -2589,10 +2589,10 @@
         <v>248</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-8.869999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D38" t="n">
         <v>500</v>
@@ -2715,10 +2715,10 @@
         <v>515</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0</v>
+        <v>-0.96</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-2.91</v>
+        <v>-3.85</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4820</v>
+        <v>4830</v>
       </c>
       <c r="D39" t="n">
         <v>4790</v>
@@ -2757,10 +2757,10 @@
         <v>4820</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.62</v>
+        <v>-0.83</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="D43" t="n">
         <v>525</v>
@@ -2925,10 +2925,10 @@
         <v>525</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>19.32</v>
+        <v>24.41</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>19.32</v>
+        <v>24.41</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D44" t="n">
         <v>675</v>
@@ -2967,10 +2967,10 @@
         <v>685</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-0.74</v>
+        <v>-1.46</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>750</v>
+        <v>630</v>
       </c>
       <c r="D45" t="n">
         <v>785</v>
@@ -3009,10 +3009,10 @@
         <v>785</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4.67</v>
+        <v>24.6</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4.67</v>
+        <v>24.6</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D46" t="n">
         <v>102</v>
@@ -3051,10 +3051,10 @@
         <v>109</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-6.42</v>
+        <v>-5.56</v>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D47" t="n">
         <v>139</v>
@@ -3093,14 +3093,14 @@
         <v>147</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>5</v>
+        <v>6.52</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.72</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4120</v>
+        <v>3300</v>
       </c>
       <c r="D48" t="n">
         <v>4120</v>
@@ -3135,14 +3135,14 @@
         <v>4120</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0</v>
+        <v>24.85</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>24.85</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5500</v>
+        <v>5300</v>
       </c>
       <c r="D50" t="n">
         <v>5325</v>
@@ -3219,14 +3219,14 @@
         <v>5800</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>5.45</v>
+        <v>9.43</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-3.18</v>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.47</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D51" t="n">
         <v>154</v>
@@ -3261,10 +3261,10 @@
         <v>164</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.61</v>
+        <v>-0.61</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-5.52</v>
+        <v>-6.67</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D52" t="n">
         <v>214</v>
@@ -3303,10 +3303,10 @@
         <v>220</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.92</v>
+        <v>2.8</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-1.83</v>
+        <v>0</v>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>

--- a/data/performance/daily/signal_list_2026-05-29.xlsx
+++ b/data/performance/daily/signal_list_2026-05-29.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,14 +469,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Swing Signal List — 2026-05-29</t>
+          <t>Swing — Review sesi market 2026-05-29</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 31.2%  (5W / 11L of 16 evaluated, 1 pending)</t>
+          <t>Win Rate: 29.6%  (8W / 19L of 27 evaluated)</t>
         </is>
       </c>
     </row>
@@ -535,39 +535,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>BBTN.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>PRE_MARKUP</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v/>
+        <v>1340</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>1270</v>
       </c>
       <c r="E5" t="n">
-        <v/>
+        <v>1345</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v/>
+        <v>0.37</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v/>
+        <v>-5.22</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>BTPN.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,19 +586,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1940</v>
+        <v>2350</v>
       </c>
       <c r="D6" t="n">
-        <v>1930</v>
+        <v>2340</v>
       </c>
       <c r="E6" t="n">
-        <v>2220</v>
+        <v>2360</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.43</v>
+        <v>0.43</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.52</v>
+        <v>-0.43</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -597,7 +607,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -618,28 +628,28 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>157</v>
+      </c>
+      <c r="D7" t="n">
         <v>156</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>159</v>
       </c>
-      <c r="E7" t="n">
-        <v>160</v>
-      </c>
       <c r="F7" s="4" t="n">
-        <v>2.56</v>
+        <v>1.27</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.64</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -651,7 +661,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GGRM.JK</t>
+          <t>MAPI.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -660,19 +670,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17000</v>
+        <v>1500</v>
       </c>
       <c r="D8" t="n">
-        <v>16950</v>
+        <v>1495</v>
       </c>
       <c r="E8" t="n">
-        <v>17075</v>
+        <v>1505</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.44</v>
+        <v>0.33</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -681,7 +691,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -693,7 +703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JTPE.JK</t>
+          <t>MBSS.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -702,28 +712,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>645</v>
+        <v>2450</v>
       </c>
       <c r="D9" t="n">
-        <v>620</v>
+        <v>2460</v>
       </c>
       <c r="E9" t="n">
-        <v>650</v>
+        <v>2500</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.78</v>
+        <v>2.04</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.88</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.41</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -735,37 +745,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MAPI.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1495</v>
+        <v>1090</v>
       </c>
       <c r="D10" t="n">
-        <v>1485</v>
+        <v>1135</v>
       </c>
       <c r="E10" t="n">
-        <v>1500</v>
+        <v>1145</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.33</v>
+        <v>5.05</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.13</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -777,7 +787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PANS.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -786,28 +796,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1735</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>1740</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>1750</v>
+        <v>85</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.86</v>
+        <v>21.43</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-8.57</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -819,28 +829,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UNIC.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13550</v>
+        <v>830</v>
       </c>
       <c r="D12" t="n">
-        <v>12750</v>
+        <v>710</v>
       </c>
       <c r="E12" t="n">
-        <v>13500</v>
+        <v>770</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.37</v>
+        <v>-7.23</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.9</v>
+        <v>-14.46</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -849,7 +859,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -861,7 +871,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JMAS.JK</t>
+          <t>UNIC.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -870,28 +880,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>282</v>
+        <v>15350</v>
       </c>
       <c r="D13" t="n">
-        <v>288</v>
+        <v>13550</v>
       </c>
       <c r="E13" t="n">
-        <v>288</v>
+        <v>14100</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.13</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-11.73</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -903,7 +913,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>CASA.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -912,19 +922,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>212</v>
+        <v>1350</v>
       </c>
       <c r="D14" t="n">
-        <v>181</v>
+        <v>1350</v>
       </c>
       <c r="E14" t="n">
-        <v>252</v>
+        <v>1355</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18.87</v>
+        <v>0.37</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-14.62</v>
+        <v>0</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -933,7 +943,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -945,7 +955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PPGL.JK</t>
+          <t>JMAS.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -954,28 +964,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="D15" t="n">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="E15" t="n">
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.8</v>
+        <v>6.02</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>6.02</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -987,37 +997,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UVCR.JK</t>
+          <t>LCKM.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>PRE_MARKUP</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>238</v>
+        <v>110</v>
       </c>
       <c r="D16" t="n">
-        <v>242</v>
+        <v>106</v>
       </c>
       <c r="E16" t="n">
-        <v>250</v>
+        <v>112</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.04</v>
+        <v>1.82</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-3.64</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1029,7 +1039,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMNT.JK</t>
+          <t>GGRP.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1038,19 +1048,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>815</v>
+        <v>294</v>
       </c>
       <c r="D17" t="n">
-        <v>800</v>
+        <v>292</v>
       </c>
       <c r="E17" t="n">
-        <v>820</v>
+        <v>300</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.61</v>
+        <v>2.04</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.84</v>
+        <v>-0.68</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1059,7 +1069,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1071,7 +1081,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1080,19 +1090,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>300</v>
+        <v>76</v>
       </c>
       <c r="D18" t="n">
-        <v>282</v>
+        <v>71</v>
       </c>
       <c r="E18" t="n">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4</v>
+        <v>7.89</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6</v>
+        <v>-6.58</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -1101,7 +1111,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1113,7 +1123,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CMRY.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1122,28 +1132,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4830</v>
+        <v>500</v>
       </c>
       <c r="D19" t="n">
-        <v>4790</v>
+        <v>545</v>
       </c>
       <c r="E19" t="n">
-        <v>4820</v>
+        <v>550</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.21</v>
+        <v>10</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>9</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1155,7 +1165,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>HBAT.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1164,28 +1174,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>422</v>
+        <v>505</v>
       </c>
       <c r="D20" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="E20" t="n">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>24.41</v>
+        <v>1.98</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.99</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1197,40 +1207,460 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>CPIN.JK</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4480</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4270</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4440</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DMAS.JK</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>157</v>
+      </c>
+      <c r="D22" t="n">
+        <v>156</v>
+      </c>
+      <c r="E22" t="n">
+        <v>159</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MAPI.JK</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1505</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MPMX.JK</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BREAKOUT</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1090</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1135</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1145</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UNIC.JK</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15350</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13550</v>
+      </c>
+      <c r="E25" t="n">
+        <v>14100</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-11.73</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DFAM.JK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>118</v>
+      </c>
+      <c r="D26" t="n">
+        <v>107</v>
+      </c>
+      <c r="E26" t="n">
+        <v>119</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>-9.32</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PPGL.JK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>234</v>
+      </c>
+      <c r="D27" t="n">
+        <v>250</v>
+      </c>
+      <c r="E27" t="n">
+        <v>256</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WMPP.JK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>36</v>
+      </c>
+      <c r="D28" t="n">
+        <v>36</v>
+      </c>
+      <c r="E28" t="n">
+        <v>36</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MMIX.JK</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>386</v>
+      </c>
+      <c r="D29" t="n">
+        <v>422</v>
+      </c>
+      <c r="E29" t="n">
+        <v>430</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>HBAT.JK</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>PRE_MARKUP</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C30" t="n">
+        <v>505</v>
+      </c>
+      <c r="D30" t="n">
         <v>500</v>
       </c>
-      <c r="D21" t="n">
-        <v>450</v>
-      </c>
-      <c r="E21" t="n">
-        <v>500</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="E30" t="n">
+        <v>515</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RGAS.JK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" t="n">
+        <v>103</v>
+      </c>
+      <c r="E31" t="n">
+        <v>105</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1247,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1265,14 +1695,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scalping Signal List — 2026-05-29</t>
+          <t>Scalping — Review sesi market 2026-05-29</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 39.1%  (18W / 28L of 46 evaluated, 2 pending)</t>
+          <t>Win Rate: 37.8%  (17W / 28L of 45 evaluated)</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1761,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALKA.JK</t>
+          <t>APLI.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1340,28 +1770,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>550</v>
+        <v>262</v>
       </c>
       <c r="D5" t="n">
-        <v>685</v>
+        <v>262</v>
       </c>
       <c r="E5" t="n">
-        <v>685</v>
+        <v>262</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>24.55</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>24.55</v>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1373,7 +1803,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARTA.JK</t>
+          <t>BBTN.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1382,28 +1812,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2330</v>
+        <v>1340</v>
       </c>
       <c r="D6" t="n">
-        <v>2760</v>
+        <v>1270</v>
       </c>
       <c r="E6" t="n">
-        <v>2910</v>
+        <v>1345</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>24.89</v>
+        <v>0.37</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-5.22</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1415,7 +1845,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BINA.JK</t>
+          <t>BMSR.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1424,19 +1854,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4390</v>
+        <v>302</v>
       </c>
       <c r="D7" t="n">
-        <v>3950</v>
+        <v>296</v>
       </c>
       <c r="E7" t="n">
-        <v>4070</v>
+        <v>302</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.29</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.02</v>
+        <v>-1.99</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -1445,7 +1875,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1457,7 +1887,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BKDP.JK</t>
+          <t>BTPN.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1466,30 +1896,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v/>
+        <v>2350</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>2340</v>
       </c>
       <c r="E8" t="n">
-        <v/>
+        <v>2360</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v/>
+        <v>-0.43</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BLTZ.JK</t>
+          <t>CTBN.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1498,30 +1938,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v/>
+        <v>5800</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>5850</v>
       </c>
       <c r="E9" t="n">
-        <v/>
+        <v>5850</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v/>
+        <v>0.86</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v/>
+        <v>0.86</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRPT.JK</t>
+          <t>DUTI.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1530,19 +1980,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1940</v>
+        <v>4330</v>
       </c>
       <c r="D10" t="n">
-        <v>1930</v>
+        <v>4100</v>
       </c>
       <c r="E10" t="n">
-        <v>2220</v>
+        <v>4100</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.43</v>
+        <v>-5.31</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.52</v>
+        <v>-5.31</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -1551,7 +2001,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1563,7 +2013,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CTBN.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1572,19 +2022,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5850</v>
+        <v>1440</v>
       </c>
       <c r="D11" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="E11" t="n">
-        <v>6050</v>
+        <v>1505</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.42</v>
+        <v>4.51</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.56</v>
+        <v>4.17</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -1593,7 +2043,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1605,7 +2055,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DMAS.JK</t>
+          <t>MBSS.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1614,19 +2064,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>2450</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>2460</v>
       </c>
       <c r="E12" t="n">
-        <v>160</v>
+        <v>2500</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.92</v>
+        <v>0.41</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -1635,7 +2085,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1647,7 +2097,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DNET.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1656,28 +2106,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10950</v>
+        <v>1090</v>
       </c>
       <c r="D13" t="n">
-        <v>9900</v>
+        <v>1135</v>
       </c>
       <c r="E13" t="n">
-        <v>10400</v>
+        <v>1145</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.02</v>
+        <v>5.05</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-9.59</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.13</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1689,7 +2139,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>TALF.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1698,28 +2148,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1500</v>
+        <v>830</v>
       </c>
       <c r="D14" t="n">
-        <v>1665</v>
+        <v>710</v>
       </c>
       <c r="E14" t="n">
-        <v>1690</v>
+        <v>770</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12.67</v>
+        <v>-7.23</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-14.46</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1731,7 +2181,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GGRM.JK</t>
+          <t>UNIC.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1740,19 +2190,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17000</v>
+        <v>15350</v>
       </c>
       <c r="D15" t="n">
-        <v>16950</v>
+        <v>13550</v>
       </c>
       <c r="E15" t="n">
-        <v>17075</v>
+        <v>14100</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.44</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.29</v>
+        <v>-11.73</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1761,7 +2211,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1773,7 +2223,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JTPE.JK</t>
+          <t>BRIS.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1782,28 +2232,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>645</v>
+        <v>1930</v>
       </c>
       <c r="D16" t="n">
-        <v>620</v>
+        <v>1980</v>
       </c>
       <c r="E16" t="n">
-        <v>650</v>
+        <v>1980</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.78</v>
+        <v>2.59</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.88</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>2.59</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1815,7 +2265,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MPMX.JK</t>
+          <t>CARS.JK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1824,28 +2274,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1135</v>
+        <v>91</v>
       </c>
       <c r="D17" t="n">
-        <v>1130</v>
+        <v>92</v>
       </c>
       <c r="E17" t="n">
-        <v>1150</v>
+        <v>96</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.32</v>
+        <v>5.49</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.1</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1857,7 +2307,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MRAT.JK</t>
+          <t>JMAS.JK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1866,28 +2316,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>450</v>
+        <v>266</v>
       </c>
       <c r="D18" t="n">
-        <v>444</v>
+        <v>282</v>
       </c>
       <c r="E18" t="n">
-        <v>450</v>
+        <v>282</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.33</v>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>6.02</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1899,7 +2349,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OMRE.JK</t>
+          <t>LCKM.JK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1908,28 +2358,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1040</v>
+        <v>110</v>
       </c>
       <c r="D19" t="n">
-        <v>1100</v>
+        <v>106</v>
       </c>
       <c r="E19" t="n">
-        <v>1300</v>
+        <v>112</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>25</v>
+        <v>1.82</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-3.64</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1941,7 +2391,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTRO.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1950,28 +2400,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4670</v>
+        <v>2520</v>
       </c>
       <c r="D20" t="n">
-        <v>4800</v>
+        <v>2150</v>
       </c>
       <c r="E20" t="n">
-        <v>5450</v>
+        <v>2580</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>16.7</v>
+        <v>2.38</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-14.68</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1983,7 +2433,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PUDP.JK</t>
+          <t>GGRP.JK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1992,19 +2442,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="D21" t="n">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="E21" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.29</v>
+        <v>-0.68</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -2013,7 +2463,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2025,7 +2475,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2034,28 +2484,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3740</v>
+        <v>500</v>
       </c>
       <c r="D22" t="n">
-        <v>3720</v>
+        <v>545</v>
       </c>
       <c r="E22" t="n">
-        <v>4020</v>
+        <v>550</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>7.49</v>
+        <v>10</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>9</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2067,7 +2517,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STTP.JK</t>
+          <t>LAJU.JK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2076,19 +2526,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10200</v>
+        <v>70</v>
       </c>
       <c r="D23" t="n">
-        <v>10200</v>
+        <v>69</v>
       </c>
       <c r="E23" t="n">
-        <v>10200</v>
+        <v>70</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0</v>
+        <v>-1.43</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -2097,7 +2547,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2109,7 +2559,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TIRT.JK</t>
+          <t>HBAT.JK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2118,28 +2568,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="D24" t="n">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="E24" t="n">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>9.31</v>
+        <v>1.98</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>9.31</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.99</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2151,7 +2601,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TLKM.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2160,19 +2610,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3030</v>
+        <v>139</v>
       </c>
       <c r="D25" t="n">
-        <v>2950</v>
+        <v>138</v>
       </c>
       <c r="E25" t="n">
-        <v>3020</v>
+        <v>148</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.33</v>
+        <v>6.47</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.64</v>
+        <v>-0.72</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -2181,7 +2631,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2193,7 +2643,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>APLI.JK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2202,19 +2652,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>336</v>
+        <v>262</v>
       </c>
       <c r="D26" t="n">
-        <v>334</v>
+        <v>262</v>
       </c>
       <c r="E26" t="n">
-        <v>356</v>
+        <v>262</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -2223,7 +2673,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2235,7 +2685,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JMAS.JK</t>
+          <t>ARTA.JK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2244,28 +2694,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>282</v>
+        <v>2500</v>
       </c>
       <c r="D27" t="n">
-        <v>288</v>
+        <v>2330</v>
       </c>
       <c r="E27" t="n">
-        <v>288</v>
+        <v>2920</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.13</v>
+        <v>16.8</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-6.8</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2277,7 +2727,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INPS.JK</t>
+          <t>BLTZ.JK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2286,19 +2736,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>750</v>
+        <v>2910</v>
       </c>
       <c r="D28" t="n">
-        <v>750</v>
+        <v>2890</v>
       </c>
       <c r="E28" t="n">
-        <v>750</v>
+        <v>2890</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -2307,7 +2757,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2319,7 +2769,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>CPIN.JK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2328,19 +2778,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>640</v>
+        <v>4480</v>
       </c>
       <c r="D29" t="n">
-        <v>625</v>
+        <v>4270</v>
       </c>
       <c r="E29" t="n">
-        <v>650</v>
+        <v>4440</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.56</v>
+        <v>-0.89</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.34</v>
+        <v>-4.69</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
@@ -2349,7 +2799,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2361,7 +2811,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SFAN.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2370,28 +2820,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1960</v>
+        <v>1440</v>
       </c>
       <c r="D30" t="n">
-        <v>1955</v>
+        <v>1500</v>
       </c>
       <c r="E30" t="n">
-        <v>1960</v>
+        <v>1505</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.17</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2403,7 +2853,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2412,28 +2862,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>212</v>
+        <v>1090</v>
       </c>
       <c r="D31" t="n">
-        <v>181</v>
+        <v>1135</v>
       </c>
       <c r="E31" t="n">
-        <v>252</v>
+        <v>1145</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>18.87</v>
+        <v>5.05</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-14.62</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.13</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2445,7 +2895,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SINI.JK</t>
+          <t>PGAS.JK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2454,19 +2904,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12325</v>
+        <v>1895</v>
       </c>
       <c r="D32" t="n">
-        <v>12000</v>
+        <v>1825</v>
       </c>
       <c r="E32" t="n">
-        <v>13000</v>
+        <v>1920</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.48</v>
+        <v>1.32</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.64</v>
+        <v>-3.69</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -2475,7 +2925,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2487,7 +2937,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KEJU.JK</t>
+          <t>PTIS.JK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2496,28 +2946,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>600</v>
+        <v>314</v>
       </c>
       <c r="D33" t="n">
-        <v>625</v>
+        <v>298</v>
       </c>
       <c r="E33" t="n">
-        <v>640</v>
+        <v>318</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.67</v>
+        <v>1.27</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-5.1</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2529,7 +2979,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOFA.JK</t>
+          <t>RDTX.JK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2538,19 +2988,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>400</v>
+        <v>16850</v>
       </c>
       <c r="D34" t="n">
-        <v>360</v>
+        <v>16675</v>
       </c>
       <c r="E34" t="n">
-        <v>426</v>
+        <v>16750</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.5</v>
+        <v>-0.59</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10</v>
+        <v>-1.04</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
@@ -2559,7 +3009,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2571,7 +3021,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PPGL.JK</t>
+          <t>TFCO.JK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2580,19 +3030,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>250</v>
+        <v>650</v>
       </c>
       <c r="D35" t="n">
-        <v>226</v>
+        <v>600</v>
       </c>
       <c r="E35" t="n">
-        <v>248</v>
+        <v>640</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.8</v>
+        <v>-1.54</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-9.6</v>
+        <v>-7.69</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -2601,7 +3051,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2613,7 +3063,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UVCR.JK</t>
+          <t>TLKM.JK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2622,28 +3072,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>238</v>
+        <v>3090</v>
       </c>
       <c r="D36" t="n">
-        <v>242</v>
+        <v>3030</v>
       </c>
       <c r="E36" t="n">
-        <v>250</v>
+        <v>3170</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5.04</v>
+        <v>2.59</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.94</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2655,7 +3105,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>UNIC.JK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,19 +3114,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>300</v>
+        <v>15350</v>
       </c>
       <c r="D37" t="n">
-        <v>282</v>
+        <v>13550</v>
       </c>
       <c r="E37" t="n">
-        <v>312</v>
+        <v>14100</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-6</v>
+        <v>-11.73</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
@@ -2685,7 +3135,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2697,7 +3147,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2706,19 +3156,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>520</v>
+        <v>820</v>
       </c>
       <c r="D38" t="n">
-        <v>500</v>
+        <v>795</v>
       </c>
       <c r="E38" t="n">
-        <v>515</v>
+        <v>820</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.96</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-3.85</v>
+        <v>-3.05</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
@@ -2727,7 +3177,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2739,7 +3189,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CMRY.JK</t>
+          <t>INPS.JK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2748,28 +3198,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4830</v>
+        <v>720</v>
       </c>
       <c r="D39" t="n">
-        <v>4790</v>
+        <v>750</v>
       </c>
       <c r="E39" t="n">
-        <v>4820</v>
+        <v>750</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>-0.21</v>
+        <v>4.17</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.17</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2781,7 +3231,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WGSH.JK</t>
+          <t>DFAM.JK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2790,28 +3240,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D40" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E40" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>8.73</v>
+        <v>0.85</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-9.32</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2823,7 +3273,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>SATU.JK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2832,28 +3282,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>336</v>
+        <v>264</v>
       </c>
       <c r="D41" t="n">
-        <v>382</v>
+        <v>258</v>
       </c>
       <c r="E41" t="n">
-        <v>386</v>
+        <v>264</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>14.88</v>
+        <v>0</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-2.27</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2865,7 +3315,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>PPGL.JK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2874,28 +3324,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>545</v>
+        <v>234</v>
       </c>
       <c r="D42" t="n">
-        <v>545</v>
+        <v>250</v>
       </c>
       <c r="E42" t="n">
-        <v>550</v>
+        <v>256</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.92</v>
+        <v>9.4</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>6.84</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2907,7 +3357,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>WGSH.JK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2916,19 +3366,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>422</v>
+        <v>115</v>
       </c>
       <c r="D43" t="n">
-        <v>525</v>
+        <v>126</v>
       </c>
       <c r="E43" t="n">
-        <v>525</v>
+        <v>126</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>24.41</v>
+        <v>9.57</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>24.41</v>
+        <v>9.57</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
@@ -2937,7 +3387,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2949,7 +3399,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SUNI.JK</t>
+          <t>GULA.JK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2958,28 +3408,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>685</v>
+        <v>500</v>
       </c>
       <c r="D44" t="n">
-        <v>675</v>
+        <v>545</v>
       </c>
       <c r="E44" t="n">
-        <v>685</v>
+        <v>550</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>9</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2991,7 +3441,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CUAN.JK</t>
+          <t>MMIX.JK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3000,19 +3450,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>630</v>
+        <v>386</v>
       </c>
       <c r="D45" t="n">
-        <v>785</v>
+        <v>422</v>
       </c>
       <c r="E45" t="n">
-        <v>785</v>
+        <v>430</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>24.6</v>
+        <v>11.4</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>24.6</v>
+        <v>9.33</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
@@ -3021,7 +3471,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3033,7 +3483,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JATI.JK</t>
+          <t>HBAT.JK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3042,19 +3492,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>108</v>
+        <v>505</v>
       </c>
       <c r="D46" t="n">
-        <v>102</v>
+        <v>500</v>
       </c>
       <c r="E46" t="n">
-        <v>109</v>
+        <v>515</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.93</v>
+        <v>1.98</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-5.56</v>
+        <v>-0.99</v>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
@@ -3063,7 +3513,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3084,28 +3534,28 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>139</v>
+      </c>
+      <c r="D47" t="n">
         <v>138</v>
       </c>
-      <c r="D47" t="n">
-        <v>139</v>
-      </c>
       <c r="E47" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>6.52</v>
+        <v>6.47</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.72</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3117,7 +3567,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BREN.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3126,19 +3576,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3300</v>
+        <v>100</v>
       </c>
       <c r="D48" t="n">
-        <v>4120</v>
+        <v>103</v>
       </c>
       <c r="E48" t="n">
-        <v>4120</v>
+        <v>105</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>24.85</v>
+        <v>5</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>24.85</v>
+        <v>3</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
@@ -3147,7 +3597,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3159,7 +3609,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MDIY.JK</t>
+          <t>AWAN.JK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3168,157 +3618,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>885</v>
+        <v>160</v>
       </c>
       <c r="D49" t="n">
-        <v>875</v>
+        <v>165</v>
       </c>
       <c r="E49" t="n">
-        <v>895</v>
+        <v>165</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1.13</v>
+        <v>3.12</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>3.12</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>RATU.JK</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SCALPING_HIGH</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>5300</v>
-      </c>
-      <c r="D50" t="n">
-        <v>5325</v>
-      </c>
-      <c r="E50" t="n">
-        <v>5800</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>AWAN.JK</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>SCALPING_HIGH</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>165</v>
-      </c>
-      <c r="D51" t="n">
-        <v>154</v>
-      </c>
-      <c r="E51" t="n">
-        <v>164</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>-6.67</v>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ADMG.JK</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>SCALPING_HIGH</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>214</v>
-      </c>
-      <c r="D52" t="n">
-        <v>214</v>
-      </c>
-      <c r="E52" t="n">
-        <v>220</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-05-29.xlsx
+++ b/data/performance/daily/signal_list_2026-05-29.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-29.xlsx
+++ b/data/performance/daily/signal_list_2026-05-29.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-29.xlsx
+++ b/data/performance/daily/signal_list_2026-05-29.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,15 +566,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -602,15 +613,20 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -644,15 +660,20 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -686,15 +707,20 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -768,17 +799,22 @@
       <c r="G10" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -812,15 +848,20 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>-14.46</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -894,17 +940,22 @@
       <c r="G13" s="4" t="n">
         <v>-11.73</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -938,15 +989,20 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -978,17 +1034,22 @@
       <c r="G15" s="4" t="n">
         <v>6.02</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1022,15 +1083,20 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1064,15 +1130,20 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1106,15 +1177,20 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1146,17 +1222,22 @@
       <c r="G19" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1190,15 +1271,20 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1230,17 +1316,22 @@
       <c r="G21" s="4" t="n">
         <v>-4.69</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1274,15 +1365,20 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1316,15 +1412,20 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,17 +1457,22 @@
       <c r="G24" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1398,17 +1504,22 @@
       <c r="G25" s="4" t="n">
         <v>-11.73</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1442,15 +1553,20 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1482,17 +1598,22 @@
       <c r="G27" s="4" t="n">
         <v>6.84</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1524,17 +1645,22 @@
       <c r="G28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1566,17 +1692,22 @@
       <c r="G29" s="4" t="n">
         <v>9.33</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1610,15 +1741,20 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1650,17 +1786,22 @@
       <c r="G31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1677,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1687,9 +1828,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1719,7 +1861,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1744,15 +1886,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1784,17 +1931,22 @@
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1828,15 +1980,20 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1868,17 +2025,22 @@
       <c r="G7" s="4" t="n">
         <v>-1.99</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1912,15 +2074,20 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1952,17 +2119,22 @@
       <c r="G9" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1994,17 +2166,22 @@
       <c r="G10" s="4" t="n">
         <v>-5.31</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2036,17 +2213,22 @@
       <c r="G11" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2078,17 +2260,22 @@
       <c r="G12" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2120,17 +2307,22 @@
       <c r="G13" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2162,17 +2354,22 @@
       <c r="G14" s="4" t="n">
         <v>-14.46</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2204,17 +2401,22 @@
       <c r="G15" s="4" t="n">
         <v>-11.73</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2246,17 +2448,22 @@
       <c r="G16" s="4" t="n">
         <v>2.59</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2288,17 +2495,22 @@
       <c r="G17" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2330,17 +2542,22 @@
       <c r="G18" s="4" t="n">
         <v>6.02</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2374,15 +2591,20 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2416,15 +2638,20 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2458,15 +2685,20 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2498,17 +2730,22 @@
       <c r="G22" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2540,17 +2777,22 @@
       <c r="G23" s="4" t="n">
         <v>-1.43</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2584,15 +2826,20 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2626,15 +2873,20 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2666,17 +2918,22 @@
       <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2710,15 +2967,20 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2750,17 +3012,22 @@
       <c r="G28" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2792,17 +3059,22 @@
       <c r="G29" s="4" t="n">
         <v>-4.69</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2834,17 +3106,22 @@
       <c r="G30" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2876,17 +3153,22 @@
       <c r="G31" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2920,15 +3202,20 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2962,15 +3249,20 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3002,17 +3294,22 @@
       <c r="G34" s="4" t="n">
         <v>-1.04</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3044,17 +3341,22 @@
       <c r="G35" s="4" t="n">
         <v>-7.69</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3088,15 +3390,20 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3128,17 +3435,22 @@
       <c r="G37" s="4" t="n">
         <v>-11.73</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3170,17 +3482,22 @@
       <c r="G38" s="4" t="n">
         <v>-3.05</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3212,17 +3529,22 @@
       <c r="G39" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3256,15 +3578,20 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3296,17 +3623,22 @@
       <c r="G41" s="4" t="n">
         <v>-2.27</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3338,17 +3670,22 @@
       <c r="G42" s="4" t="n">
         <v>6.84</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3380,17 +3717,22 @@
       <c r="G43" s="4" t="n">
         <v>9.57</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3422,17 +3764,22 @@
       <c r="G44" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3464,17 +3811,22 @@
       <c r="G45" s="4" t="n">
         <v>9.33</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3508,15 +3860,20 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3550,15 +3907,20 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3590,17 +3952,22 @@
       <c r="G48" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3632,17 +3999,22 @@
       <c r="G49" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-05-29.xlsx
+++ b/data/performance/daily/signal_list_2026-05-29.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>1340</v>
       </c>
       <c r="D5" t="n">
+        <v>1335</v>
+      </c>
+      <c r="E5" t="n">
         <v>1270</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1345</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-5.22</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>2350</v>
       </c>
       <c r="D6" t="n">
+        <v>2350</v>
+      </c>
+      <c r="E6" t="n">
         <v>2340</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>2360</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-0.43</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>157</v>
       </c>
       <c r="D7" t="n">
+        <v>158</v>
+      </c>
+      <c r="E7" t="n">
         <v>156</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>159</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>1500</v>
       </c>
       <c r="D8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E8" t="n">
         <v>1495</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1505</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.33</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>2450</v>
       </c>
       <c r="D9" t="n">
+        <v>2490</v>
+      </c>
+      <c r="E9" t="n">
         <v>2460</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>2500</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>2.04</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>1090</v>
       </c>
       <c r="D10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E10" t="n">
         <v>1135</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1145</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>5.05</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>70</v>
       </c>
       <c r="D11" t="n">
+        <v>83</v>
+      </c>
+      <c r="E11" t="n">
         <v>64</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>85</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>21.43</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-8.57</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>830</v>
       </c>
       <c r="D12" t="n">
+        <v>760</v>
+      </c>
+      <c r="E12" t="n">
         <v>710</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>770</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>-7.23</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-14.46</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>15350</v>
       </c>
       <c r="D13" t="n">
+        <v>13525</v>
+      </c>
+      <c r="E13" t="n">
         <v>13550</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>14100</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>-8.140000000000001</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-11.73</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -979,30 +1012,33 @@
         <v>1350</v>
       </c>
       <c r="E14" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F14" t="n">
         <v>1355</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>266</v>
       </c>
       <c r="D15" t="n">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="E15" t="n">
         <v>282</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>6.02</v>
+      <c r="F15" t="n">
+        <v>282</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>6.02</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H15" s="4" t="n">
+        <v>6.02</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>110</v>
       </c>
       <c r="D16" t="n">
+        <v>107</v>
+      </c>
+      <c r="E16" t="n">
         <v>106</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>112</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-3.64</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>294</v>
       </c>
       <c r="D17" t="n">
+        <v>294</v>
+      </c>
+      <c r="E17" t="n">
         <v>292</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>300</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>2.04</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-0.68</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>76</v>
       </c>
       <c r="D18" t="n">
+        <v>74</v>
+      </c>
+      <c r="E18" t="n">
         <v>71</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>82</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>7.89</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-6.58</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>500</v>
       </c>
       <c r="D19" t="n">
+        <v>500</v>
+      </c>
+      <c r="E19" t="n">
         <v>545</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>550</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1258,33 +1309,36 @@
         <v>505</v>
       </c>
       <c r="D20" t="n">
+        <v>515</v>
+      </c>
+      <c r="E20" t="n">
         <v>500</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>515</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>1.98</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-0.99</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>4480</v>
       </c>
       <c r="D21" t="n">
+        <v>4420</v>
+      </c>
+      <c r="E21" t="n">
         <v>4270</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>4440</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-4.69</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1352,33 +1409,36 @@
         <v>157</v>
       </c>
       <c r="D22" t="n">
+        <v>158</v>
+      </c>
+      <c r="E22" t="n">
         <v>156</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>159</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1399,33 +1459,36 @@
         <v>1500</v>
       </c>
       <c r="D23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E23" t="n">
         <v>1495</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>1505</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-0.33</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1446,33 +1509,36 @@
         <v>1090</v>
       </c>
       <c r="D24" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E24" t="n">
         <v>1135</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>1145</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>5.05</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1493,33 +1559,36 @@
         <v>15350</v>
       </c>
       <c r="D25" t="n">
+        <v>13525</v>
+      </c>
+      <c r="E25" t="n">
         <v>13550</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>14100</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>-8.140000000000001</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-11.73</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1540,33 +1609,36 @@
         <v>118</v>
       </c>
       <c r="D26" t="n">
+        <v>118</v>
+      </c>
+      <c r="E26" t="n">
         <v>107</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>119</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-9.32</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1587,33 +1659,36 @@
         <v>234</v>
       </c>
       <c r="D27" t="n">
+        <v>232</v>
+      </c>
+      <c r="E27" t="n">
         <v>250</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>256</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>9.4</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>6.84</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1639,28 +1714,31 @@
       <c r="E28" t="n">
         <v>36</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>0</v>
+      <c r="F28" t="n">
+        <v>36</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H28" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1681,33 +1759,36 @@
         <v>386</v>
       </c>
       <c r="D29" t="n">
+        <v>388</v>
+      </c>
+      <c r="E29" t="n">
         <v>422</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>430</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>11.4</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>9.33</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1728,33 +1809,36 @@
         <v>505</v>
       </c>
       <c r="D30" t="n">
+        <v>515</v>
+      </c>
+      <c r="E30" t="n">
         <v>500</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>515</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>1.98</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-0.99</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1775,33 +1859,36 @@
         <v>100</v>
       </c>
       <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="n">
         <v>103</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>105</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1818,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1826,12 +1913,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1861,45 +1949,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1925,28 +2018,31 @@
       <c r="E5" t="n">
         <v>262</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
+      <c r="F5" t="n">
+        <v>262</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>1340</v>
       </c>
       <c r="D6" t="n">
+        <v>1335</v>
+      </c>
+      <c r="E6" t="n">
         <v>1270</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1345</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-5.22</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2014,33 +2113,36 @@
         <v>302</v>
       </c>
       <c r="D7" t="n">
+        <v>302</v>
+      </c>
+      <c r="E7" t="n">
         <v>296</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>302</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-1.99</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2061,33 +2163,36 @@
         <v>2350</v>
       </c>
       <c r="D8" t="n">
+        <v>2350</v>
+      </c>
+      <c r="E8" t="n">
         <v>2340</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2360</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.43</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2108,33 +2213,36 @@
         <v>5800</v>
       </c>
       <c r="D9" t="n">
-        <v>5850</v>
+        <v>5825</v>
       </c>
       <c r="E9" t="n">
         <v>5850</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>0.86</v>
+      <c r="F9" t="n">
+        <v>5850</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H9" s="4" t="n">
+        <v>0.86</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2160,28 +2268,31 @@
       <c r="E10" t="n">
         <v>4100</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>-5.31</v>
+      <c r="F10" t="n">
+        <v>4100</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>-5.31</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H10" s="4" t="n">
+        <v>-5.31</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2202,33 +2313,36 @@
         <v>1440</v>
       </c>
       <c r="D11" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E11" t="n">
         <v>1500</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1505</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>4.51</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2249,33 +2363,36 @@
         <v>2450</v>
       </c>
       <c r="D12" t="n">
+        <v>2490</v>
+      </c>
+      <c r="E12" t="n">
         <v>2460</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>2500</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>2.04</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2296,33 +2413,36 @@
         <v>1090</v>
       </c>
       <c r="D13" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E13" t="n">
         <v>1135</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1145</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>5.05</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2343,33 +2463,36 @@
         <v>830</v>
       </c>
       <c r="D14" t="n">
+        <v>760</v>
+      </c>
+      <c r="E14" t="n">
         <v>710</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>770</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>-7.23</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-14.46</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2390,33 +2513,36 @@
         <v>15350</v>
       </c>
       <c r="D15" t="n">
+        <v>13525</v>
+      </c>
+      <c r="E15" t="n">
         <v>13550</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>14100</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>-8.140000000000001</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-11.73</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2437,33 +2563,36 @@
         <v>1930</v>
       </c>
       <c r="D16" t="n">
-        <v>1980</v>
+        <v>1930</v>
       </c>
       <c r="E16" t="n">
         <v>1980</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>2.59</v>
+      <c r="F16" t="n">
+        <v>1980</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>2.59</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H16" s="4" t="n">
+        <v>2.59</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2484,33 +2613,36 @@
         <v>91</v>
       </c>
       <c r="D17" t="n">
+        <v>91</v>
+      </c>
+      <c r="E17" t="n">
         <v>92</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>96</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>5.49</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2531,33 +2663,36 @@
         <v>266</v>
       </c>
       <c r="D18" t="n">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="E18" t="n">
         <v>282</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>6.02</v>
+      <c r="F18" t="n">
+        <v>282</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>6.02</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H18" s="4" t="n">
+        <v>6.02</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2578,33 +2713,36 @@
         <v>110</v>
       </c>
       <c r="D19" t="n">
+        <v>107</v>
+      </c>
+      <c r="E19" t="n">
         <v>106</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>112</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-3.64</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2625,33 +2763,36 @@
         <v>2520</v>
       </c>
       <c r="D20" t="n">
+        <v>2560</v>
+      </c>
+      <c r="E20" t="n">
         <v>2150</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>2580</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>2.38</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-14.68</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2672,33 +2813,36 @@
         <v>294</v>
       </c>
       <c r="D21" t="n">
+        <v>294</v>
+      </c>
+      <c r="E21" t="n">
         <v>292</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>300</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>2.04</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-0.68</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2719,33 +2863,36 @@
         <v>500</v>
       </c>
       <c r="D22" t="n">
+        <v>500</v>
+      </c>
+      <c r="E22" t="n">
         <v>545</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>550</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2766,33 +2913,36 @@
         <v>70</v>
       </c>
       <c r="D23" t="n">
+        <v>68</v>
+      </c>
+      <c r="E23" t="n">
         <v>69</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>70</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-1.43</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2813,33 +2963,36 @@
         <v>505</v>
       </c>
       <c r="D24" t="n">
+        <v>515</v>
+      </c>
+      <c r="E24" t="n">
         <v>500</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>515</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>1.98</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-0.99</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2860,33 +3013,36 @@
         <v>139</v>
       </c>
       <c r="D25" t="n">
+        <v>142</v>
+      </c>
+      <c r="E25" t="n">
         <v>138</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>148</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>6.47</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2912,28 +3068,31 @@
       <c r="E26" t="n">
         <v>262</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>0</v>
+      <c r="F26" t="n">
+        <v>262</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2954,33 +3113,36 @@
         <v>2500</v>
       </c>
       <c r="D27" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E27" t="n">
         <v>2330</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>2920</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>16.8</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>-6.8</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3006,28 +3168,31 @@
       <c r="E28" t="n">
         <v>2890</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>-0.6899999999999999</v>
+      <c r="F28" t="n">
+        <v>2890</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H28" s="4" t="n">
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3048,33 +3213,36 @@
         <v>4480</v>
       </c>
       <c r="D29" t="n">
+        <v>4420</v>
+      </c>
+      <c r="E29" t="n">
         <v>4270</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>4440</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-4.69</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3095,33 +3263,36 @@
         <v>1440</v>
       </c>
       <c r="D30" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E30" t="n">
         <v>1500</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>1505</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>4.51</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3142,33 +3313,36 @@
         <v>1090</v>
       </c>
       <c r="D31" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E31" t="n">
         <v>1135</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>1145</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>5.05</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>4.13</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3189,33 +3363,36 @@
         <v>1895</v>
       </c>
       <c r="D32" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E32" t="n">
         <v>1825</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>1920</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>1.32</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-3.69</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3236,33 +3413,36 @@
         <v>314</v>
       </c>
       <c r="D33" t="n">
+        <v>316</v>
+      </c>
+      <c r="E33" t="n">
         <v>298</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>318</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>-5.1</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3283,33 +3463,36 @@
         <v>16850</v>
       </c>
       <c r="D34" t="n">
+        <v>16700</v>
+      </c>
+      <c r="E34" t="n">
         <v>16675</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>16750</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>-0.59</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-1.04</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3330,33 +3513,36 @@
         <v>650</v>
       </c>
       <c r="D35" t="n">
+        <v>640</v>
+      </c>
+      <c r="E35" t="n">
         <v>600</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>640</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>-1.54</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-7.69</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3377,33 +3563,36 @@
         <v>3090</v>
       </c>
       <c r="D36" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E36" t="n">
         <v>3030</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>3170</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>2.59</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-1.94</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3424,33 +3613,36 @@
         <v>15350</v>
       </c>
       <c r="D37" t="n">
+        <v>13525</v>
+      </c>
+      <c r="E37" t="n">
         <v>13550</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>14100</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>-8.140000000000001</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-11.73</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3471,33 +3663,36 @@
         <v>820</v>
       </c>
       <c r="D38" t="n">
+        <v>820</v>
+      </c>
+      <c r="E38" t="n">
         <v>795</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>820</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-3.05</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3518,33 +3713,36 @@
         <v>720</v>
       </c>
       <c r="D39" t="n">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="E39" t="n">
         <v>750</v>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>4.17</v>
+      <c r="F39" t="n">
+        <v>750</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H39" s="4" t="n">
+        <v>4.17</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3565,33 +3763,36 @@
         <v>118</v>
       </c>
       <c r="D40" t="n">
+        <v>118</v>
+      </c>
+      <c r="E40" t="n">
         <v>107</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>119</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>-9.32</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3612,33 +3813,36 @@
         <v>264</v>
       </c>
       <c r="D41" t="n">
+        <v>264</v>
+      </c>
+      <c r="E41" t="n">
         <v>258</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>264</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>-2.27</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3659,33 +3863,36 @@
         <v>234</v>
       </c>
       <c r="D42" t="n">
+        <v>232</v>
+      </c>
+      <c r="E42" t="n">
         <v>250</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>256</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>9.4</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>6.84</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3706,33 +3913,36 @@
         <v>115</v>
       </c>
       <c r="D43" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E43" t="n">
         <v>126</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>9.57</v>
+      <c r="F43" t="n">
+        <v>126</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>9.57</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H43" s="4" t="n">
+        <v>9.57</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3753,33 +3963,36 @@
         <v>500</v>
       </c>
       <c r="D44" t="n">
+        <v>500</v>
+      </c>
+      <c r="E44" t="n">
         <v>545</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>550</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,33 +4013,36 @@
         <v>386</v>
       </c>
       <c r="D45" t="n">
+        <v>388</v>
+      </c>
+      <c r="E45" t="n">
         <v>422</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>430</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>11.4</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>9.33</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3847,33 +4063,36 @@
         <v>505</v>
       </c>
       <c r="D46" t="n">
+        <v>515</v>
+      </c>
+      <c r="E46" t="n">
         <v>500</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>515</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>1.98</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>-0.99</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3894,33 +4113,36 @@
         <v>139</v>
       </c>
       <c r="D47" t="n">
+        <v>142</v>
+      </c>
+      <c r="E47" t="n">
         <v>138</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>148</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>6.47</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3941,33 +4163,36 @@
         <v>100</v>
       </c>
       <c r="D48" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" t="n">
         <v>103</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>105</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3988,33 +4213,36 @@
         <v>160</v>
       </c>
       <c r="D49" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E49" t="n">
         <v>165</v>
       </c>
-      <c r="F49" s="4" t="n">
-        <v>3.12</v>
+      <c r="F49" t="n">
+        <v>165</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H49" s="4" t="n">
+        <v>3.12</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
